--- a/gstdatabase/Gross_Net_Tax_collection.xlsx
+++ b/gstdatabase/Gross_Net_Tax_collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3FB212-7C2A-405B-9BB1-398AA4CEDC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9B4F52-6FF3-47C2-A9B7-136FC5233AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="19" activeTab="27" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="19" activeTab="28" xr2:uid="{5CAD827C-DDF4-9F48-BEDE-38002A84F822}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr-24" sheetId="2" r:id="rId1"/>
@@ -41,12 +41,14 @@
     <sheet name="May-26" sheetId="27" r:id="rId26"/>
     <sheet name="Jun-26" sheetId="28" r:id="rId27"/>
     <sheet name="Jul-26" sheetId="30" r:id="rId28"/>
+    <sheet name="Aug-26" sheetId="31" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Apr-24'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'Apr-25'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Aug-24'!$A$1:$G$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'Aug-25'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="28">'Aug-26'!$A$1:$G$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Dec-24'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'Dec-25'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'Feb-26'!$A$1:$G$53</definedName>
@@ -90,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="142">
   <si>
     <t>Monthly</t>
   </si>
@@ -513,6 +515,9 @@
   </si>
   <si>
     <t xml:space="preserve">GST Gross and Net Collections as on  31/07/2026 (Amount in crores) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST Gross and Net Collections as on  31/8/2026 (Amount in crores) </t>
   </si>
 </sst>
 </file>
@@ -1575,16 +1580,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1596,11 +1604,23 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="38" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1612,18 +1632,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1640,9 +1648,6 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2013,28 +2018,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="173"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -3166,15 +3171,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3208,36 +3213,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
-      <c r="J1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="15.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170" t="s">
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
     </row>
     <row r="3" spans="1:12" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -4830,33 +4835,33 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="18">
-      <c r="A54" s="177" t="s">
+      <c r="A54" s="182" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="177"/>
-      <c r="C54" s="177"/>
-      <c r="D54" s="177"/>
+      <c r="B54" s="182"/>
+      <c r="C54" s="182"/>
+      <c r="D54" s="182"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="178" t="s">
+      <c r="A55" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="178"/>
-      <c r="C55" s="178"/>
-      <c r="D55" s="178"/>
+      <c r="B55" s="183"/>
+      <c r="C55" s="183"/>
+      <c r="D55" s="183"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="179" t="s">
+      <c r="B56" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="179"/>
-      <c r="D56" s="179"/>
+      <c r="C56" s="184"/>
+      <c r="D56" s="184"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="176" t="s">
+      <c r="A57" s="181" t="s">
         <v>88</v>
       </c>
       <c r="B57" s="100" t="s">
@@ -4865,19 +4870,19 @@
       <c r="C57" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="176" t="s">
+      <c r="D57" s="181" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="176"/>
+      <c r="A58" s="181"/>
       <c r="B58" s="100" t="s">
         <v>91</v>
       </c>
       <c r="C58" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="176"/>
+      <c r="D58" s="181"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="101" t="s">
@@ -5028,28 +5033,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -6048,28 +6053,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -7110,28 +7115,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.6">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="183"/>
-      <c r="G1" s="183"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
     </row>
     <row r="2" spans="1:13" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:13" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -8181,28 +8186,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="185" t="s">
+      <c r="C2" s="169"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="182"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -9237,28 +9242,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -10257,28 +10262,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -11284,28 +11289,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -12350,28 +12355,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="185" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="182"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -13417,28 +13422,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="185" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="182"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -14473,28 +14478,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="173"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -15589,15 +15594,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15629,28 +15634,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="186" t="s">
+      <c r="B2" s="187" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="186" t="s">
+      <c r="C2" s="188"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="187" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="187"/>
-      <c r="G2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="189"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -16696,28 +16701,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -17743,28 +17748,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -18805,28 +18810,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -19871,28 +19876,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -20910,28 +20915,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -21866,28 +21871,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="185" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="181"/>
-      <c r="G2" s="182"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -22836,28 +22841,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -23793,28 +23798,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="168" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="182"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="108"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183" t="s">
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="109" t="s">
@@ -24233,7 +24238,7 @@
       <c r="C25" s="77">
         <v>12288.0448048</v>
       </c>
-      <c r="D25" s="189"/>
+      <c r="D25" s="167"/>
       <c r="E25" s="67">
         <v>45212.624783599997</v>
       </c>
@@ -24619,6 +24624,875 @@
       </c>
       <c r="G44" s="66">
         <v>9.186300121832236E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF85E262-79C9-4DA7-890D-38A5C0B98DFE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
+    <col min="2" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A1" s="168" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="170"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.6">
+      <c r="A2" s="108"/>
+      <c r="B2" s="171" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.6">
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111">
+        <v>45870</v>
+      </c>
+      <c r="C3" s="111">
+        <v>46235</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="111">
+        <v>45870</v>
+      </c>
+      <c r="F3" s="111">
+        <v>46235</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.6">
+      <c r="A4" s="109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" collapsed="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:9" outlineLevel="1">
+      <c r="A6" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="77">
+        <v>34076.07</v>
+      </c>
+      <c r="C6" s="77">
+        <v>38412.78</v>
+      </c>
+      <c r="D6" s="150"/>
+      <c r="E6" s="67">
+        <v>188171.18</v>
+      </c>
+      <c r="F6" s="67">
+        <v>205160.55</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="128"/>
+    </row>
+    <row r="7" spans="1:9" outlineLevel="1">
+      <c r="A7" s="127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="77">
+        <v>42854.48</v>
+      </c>
+      <c r="C7" s="77">
+        <v>46315.88</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="67">
+        <v>233455.53</v>
+      </c>
+      <c r="F7" s="67">
+        <v>245786.93</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="I7" s="128"/>
+    </row>
+    <row r="8" spans="1:9" outlineLevel="1">
+      <c r="A8" s="127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="77">
+        <v>48639.27</v>
+      </c>
+      <c r="C8" s="77">
+        <v>52520.27</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="67">
+        <v>277500.76</v>
+      </c>
+      <c r="F8" s="67">
+        <v>285422.88</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="138"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="35">
+        <v>125569.82</v>
+      </c>
+      <c r="C9" s="35">
+        <v>137248.93</v>
+      </c>
+      <c r="D9" s="61">
+        <v>9.3008893378998092E-2</v>
+      </c>
+      <c r="E9" s="37">
+        <v>699127.47</v>
+      </c>
+      <c r="F9" s="37">
+        <v>736370.36</v>
+      </c>
+      <c r="G9" s="61">
+        <v>5.3270528763517122E-2</v>
+      </c>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="14"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:9" ht="12.75" customHeight="1" collapsed="1">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="9"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="1:9" outlineLevel="1">
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="141">
+        <v>48546.49</v>
+      </c>
+      <c r="C12" s="141">
+        <v>62603.809979400001</v>
+      </c>
+      <c r="D12" s="79"/>
+      <c r="E12" s="36">
+        <v>240596.06</v>
+      </c>
+      <c r="F12" s="36">
+        <v>306387.02997939999</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="35">
+        <v>48546.49</v>
+      </c>
+      <c r="C13" s="35">
+        <v>62603.809979400001</v>
+      </c>
+      <c r="D13" s="61">
+        <v>0.28956408546529322</v>
+      </c>
+      <c r="E13" s="35">
+        <v>240596.06</v>
+      </c>
+      <c r="F13" s="35">
+        <v>306387.02997939999</v>
+      </c>
+      <c r="G13" s="63">
+        <v>0.27344990595190954</v>
+      </c>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="61"/>
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.6">
+      <c r="A15" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="65">
+        <v>34076.07</v>
+      </c>
+      <c r="C15" s="65">
+        <v>38412.78</v>
+      </c>
+      <c r="D15" s="76"/>
+      <c r="E15" s="65">
+        <v>188171.18</v>
+      </c>
+      <c r="F15" s="65">
+        <v>205160.55</v>
+      </c>
+      <c r="G15" s="76"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.6">
+      <c r="A16" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="65">
+        <v>42854.48</v>
+      </c>
+      <c r="C16" s="65">
+        <v>46315.88</v>
+      </c>
+      <c r="D16" s="76"/>
+      <c r="E16" s="65">
+        <v>233455.53</v>
+      </c>
+      <c r="F16" s="65">
+        <v>245786.93</v>
+      </c>
+      <c r="G16" s="76"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.6">
+      <c r="A17" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="65">
+        <v>97185.76</v>
+      </c>
+      <c r="C17" s="65">
+        <v>115124.0799794</v>
+      </c>
+      <c r="D17" s="76"/>
+      <c r="E17" s="65">
+        <v>518096.82</v>
+      </c>
+      <c r="F17" s="65">
+        <v>591809.90997939999</v>
+      </c>
+      <c r="G17" s="76"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.6">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="40">
+        <v>174116.31</v>
+      </c>
+      <c r="C18" s="40">
+        <v>199852.73997940001</v>
+      </c>
+      <c r="D18" s="66">
+        <v>0.14781171263852322</v>
+      </c>
+      <c r="E18" s="40">
+        <v>939723.53</v>
+      </c>
+      <c r="F18" s="40">
+        <v>1042757.3899794</v>
+      </c>
+      <c r="G18" s="66">
+        <v>0.10964273713503792</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="20" customFormat="1" collapsed="1">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="104"/>
+    </row>
+    <row r="20" spans="1:9" s="20" customFormat="1" outlineLevel="1">
+      <c r="A20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="77">
+        <v>2599.6800000000003</v>
+      </c>
+      <c r="C20" s="77">
+        <v>3890.2799999999997</v>
+      </c>
+      <c r="D20" s="79"/>
+      <c r="E20" s="41">
+        <v>16554.149999999998</v>
+      </c>
+      <c r="F20" s="41">
+        <v>21734.240000000002</v>
+      </c>
+      <c r="G20" s="80"/>
+    </row>
+    <row r="21" spans="1:9" s="20" customFormat="1" outlineLevel="1">
+      <c r="A21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="77">
+        <v>3114.7799999999997</v>
+      </c>
+      <c r="C21" s="77">
+        <v>4555.49</v>
+      </c>
+      <c r="D21" s="79"/>
+      <c r="E21" s="41">
+        <v>20735.11</v>
+      </c>
+      <c r="F21" s="41">
+        <v>25857.63</v>
+      </c>
+      <c r="G21" s="80"/>
+    </row>
+    <row r="22" spans="1:9" s="20" customFormat="1" outlineLevel="1">
+      <c r="A22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="77">
+        <v>5000.12</v>
+      </c>
+      <c r="C22" s="77">
+        <v>10044.33</v>
+      </c>
+      <c r="D22" s="79"/>
+      <c r="E22" s="41">
+        <v>33062.160000000003</v>
+      </c>
+      <c r="F22" s="41">
+        <v>43333.2</v>
+      </c>
+      <c r="G22" s="80"/>
+    </row>
+    <row r="23" spans="1:9" s="20" customFormat="1">
+      <c r="A23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="35">
+        <v>10714.58</v>
+      </c>
+      <c r="C23" s="35">
+        <v>18490.099999999999</v>
+      </c>
+      <c r="D23" s="63">
+        <v>0.72569526756998393</v>
+      </c>
+      <c r="E23" s="35">
+        <v>70351.42</v>
+      </c>
+      <c r="F23" s="35">
+        <v>90925.07</v>
+      </c>
+      <c r="G23" s="63">
+        <v>0.29244114759872675</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="20" customFormat="1" collapsed="1">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="79"/>
+    </row>
+    <row r="25" spans="1:9" s="20" customFormat="1" outlineLevel="1">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="77">
+        <v>8220.83</v>
+      </c>
+      <c r="C25" s="77">
+        <v>13305.290952400001</v>
+      </c>
+      <c r="D25" s="167"/>
+      <c r="E25" s="67">
+        <v>53433.45</v>
+      </c>
+      <c r="F25" s="67">
+        <v>62309.290952400006</v>
+      </c>
+      <c r="G25" s="80"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:9" s="20" customFormat="1">
+      <c r="A26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="35">
+        <v>8220.83</v>
+      </c>
+      <c r="C26" s="35">
+        <v>13305.290952400001</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.61848511067617262</v>
+      </c>
+      <c r="E26" s="35">
+        <v>53433.45</v>
+      </c>
+      <c r="F26" s="35">
+        <v>62309.290952400006</v>
+      </c>
+      <c r="G26" s="63">
+        <v>0.16611019787043535</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26"/>
+    </row>
+    <row r="27" spans="1:9" s="20" customFormat="1">
+      <c r="A27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="21"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:9" s="20" customFormat="1">
+      <c r="A28" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="42">
+        <v>2599.6800000000003</v>
+      </c>
+      <c r="C28" s="42">
+        <v>3890.2799999999997</v>
+      </c>
+      <c r="D28" s="82"/>
+      <c r="E28" s="42">
+        <v>16554.149999999998</v>
+      </c>
+      <c r="F28" s="42">
+        <v>21734.240000000002</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="21"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:9" s="20" customFormat="1">
+      <c r="A29" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="42">
+        <v>3114.7799999999997</v>
+      </c>
+      <c r="C29" s="42">
+        <v>4555.49</v>
+      </c>
+      <c r="D29" s="82"/>
+      <c r="E29" s="42">
+        <v>20735.11</v>
+      </c>
+      <c r="F29" s="42">
+        <v>25857.63</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="21"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:9" s="20" customFormat="1">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="42">
+        <v>13220.95</v>
+      </c>
+      <c r="C30" s="42">
+        <v>23349.620952400001</v>
+      </c>
+      <c r="D30" s="82"/>
+      <c r="E30" s="42">
+        <v>86495.61</v>
+      </c>
+      <c r="F30" s="42">
+        <v>105642.4909524</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="21"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:9" s="20" customFormat="1" ht="15.6">
+      <c r="A31" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40">
+        <v>18935.41</v>
+      </c>
+      <c r="C31" s="40">
+        <v>31795.390952400001</v>
+      </c>
+      <c r="D31" s="70">
+        <v>0.67914985481698054</v>
+      </c>
+      <c r="E31" s="40">
+        <v>123784.87</v>
+      </c>
+      <c r="F31" s="40">
+        <v>153234.36095239999</v>
+      </c>
+      <c r="G31" s="70">
+        <v>0.23790864709394621</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:9" s="20" customFormat="1">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="21"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9" s="20" customFormat="1">
+      <c r="A33" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="42">
+        <v>31476.39</v>
+      </c>
+      <c r="C33" s="42">
+        <v>34522.5</v>
+      </c>
+      <c r="D33" s="134">
+        <v>0</v>
+      </c>
+      <c r="E33" s="42">
+        <v>171617.03</v>
+      </c>
+      <c r="F33" s="42">
+        <v>183426.31</v>
+      </c>
+      <c r="G33" s="82"/>
+      <c r="H33" s="21"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:9" s="20" customFormat="1">
+      <c r="A34" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="42">
+        <v>39739.700000000004</v>
+      </c>
+      <c r="C34" s="42">
+        <v>41760.39</v>
+      </c>
+      <c r="D34" s="134">
+        <v>0</v>
+      </c>
+      <c r="E34" s="42">
+        <v>212720.41999999998</v>
+      </c>
+      <c r="F34" s="42">
+        <v>219929.3</v>
+      </c>
+      <c r="G34" s="82"/>
+      <c r="H34" s="21"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9" s="20" customFormat="1">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="42">
+        <v>43639.149999999994</v>
+      </c>
+      <c r="C35" s="42">
+        <v>42475.939999999995</v>
+      </c>
+      <c r="D35" s="134">
+        <v>0</v>
+      </c>
+      <c r="E35" s="42">
+        <v>244438.6</v>
+      </c>
+      <c r="F35" s="42">
+        <v>242089.68</v>
+      </c>
+      <c r="G35" s="82"/>
+      <c r="H35" s="21"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:9" s="20" customFormat="1">
+      <c r="A36" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="43">
+        <v>114855.23999999999</v>
+      </c>
+      <c r="C36" s="43">
+        <v>118758.82999999999</v>
+      </c>
+      <c r="D36" s="63">
+        <v>3.3987043168426601E-2</v>
+      </c>
+      <c r="E36" s="43">
+        <v>628776.04999999993</v>
+      </c>
+      <c r="F36" s="43">
+        <v>645445.29</v>
+      </c>
+      <c r="G36" s="63">
+        <v>2.6510615345479716E-2</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:9" s="20" customFormat="1">
+      <c r="A37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="21"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9" s="20" customFormat="1">
+      <c r="A38" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="42">
+        <v>40325.659999999996</v>
+      </c>
+      <c r="C38" s="42">
+        <v>49298.519027000002</v>
+      </c>
+      <c r="D38" s="134">
+        <v>0</v>
+      </c>
+      <c r="E38" s="42">
+        <v>187162.61</v>
+      </c>
+      <c r="F38" s="42">
+        <v>244077.73902699997</v>
+      </c>
+      <c r="G38" s="82"/>
+      <c r="H38" s="21"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" s="20" customFormat="1">
+      <c r="A39" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="43">
+        <v>40325.659999999996</v>
+      </c>
+      <c r="C39" s="43">
+        <v>49298.519027000002</v>
+      </c>
+      <c r="D39" s="63">
+        <v>0.22250991123269914</v>
+      </c>
+      <c r="E39" s="43">
+        <v>187162.61</v>
+      </c>
+      <c r="F39" s="43">
+        <v>244077.73902699997</v>
+      </c>
+      <c r="G39" s="63">
+        <v>0.30409454659239898</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="132"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="61"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.6">
+      <c r="A41" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="65">
+        <v>31476.39</v>
+      </c>
+      <c r="C41" s="65">
+        <v>34522.5</v>
+      </c>
+      <c r="D41" s="135"/>
+      <c r="E41" s="65">
+        <v>171617.03</v>
+      </c>
+      <c r="F41" s="65">
+        <v>183426.31</v>
+      </c>
+      <c r="G41" s="76"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.6">
+      <c r="A42" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="65">
+        <v>39739.700000000004</v>
+      </c>
+      <c r="C42" s="65">
+        <v>41760.39</v>
+      </c>
+      <c r="D42" s="76"/>
+      <c r="E42" s="65">
+        <v>212720.41999999998</v>
+      </c>
+      <c r="F42" s="65">
+        <v>219929.3</v>
+      </c>
+      <c r="G42" s="76"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.6">
+      <c r="A43" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="65">
+        <v>83964.81</v>
+      </c>
+      <c r="C43" s="65">
+        <v>91774.459027000004</v>
+      </c>
+      <c r="D43" s="76"/>
+      <c r="E43" s="65">
+        <v>431601.20999999996</v>
+      </c>
+      <c r="F43" s="65">
+        <v>486167.41902699997</v>
+      </c>
+      <c r="G43" s="76"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.6">
+      <c r="A44" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="40">
+        <v>155180.9</v>
+      </c>
+      <c r="C44" s="40">
+        <v>168057.34902700002</v>
+      </c>
+      <c r="D44" s="66">
+        <v>8.2977022475059892E-2</v>
+      </c>
+      <c r="E44" s="40">
+        <v>815938.65999999992</v>
+      </c>
+      <c r="F44" s="40">
+        <v>889523.02902699995</v>
+      </c>
+      <c r="G44" s="66">
+        <v>9.0183702077555772E-2</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -24653,28 +25527,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="173"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="175" t="s">
+      <c r="C2" s="178"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="179"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -25768,15 +26642,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25804,26 +26678,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -26794,15 +27668,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26831,28 +27705,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -27847,15 +28721,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -27887,28 +28761,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -28915,15 +29789,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
     <row r="56" spans="1:7" ht="18">
       <c r="A56" s="71"/>
@@ -28958,28 +29832,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:10" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -29987,15 +30861,15 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="176" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="174"/>
-      <c r="C55" s="174"/>
-      <c r="D55" s="174"/>
-      <c r="E55" s="174"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="174"/>
+      <c r="B55" s="176"/>
+      <c r="C55" s="176"/>
+      <c r="D55" s="176"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -30028,28 +30902,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="2" t="s">
@@ -31215,28 +32089,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="180" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
     </row>
     <row r="2" spans="1:9" ht="15.6">
       <c r="A2" s="1"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="2" t="s">
